--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4FA57D-8DCE-4081-9572-FD6FD5293B20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90930D43-6377-4DFC-BA04-779F4C77248C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="77">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>FEBRUARY 2026</t>
+  </si>
+  <si>
+    <t>02/14/2026</t>
   </si>
 </sst>
 </file>
@@ -2425,7 +2428,9 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>76</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2433,22 +2438,27 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518378198</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" ref="K9:K26" si="2">M9*12</f>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" ref="L9:L26" si="3">I9-K9</f>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -2460,7 +2470,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>76</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2468,22 +2480,27 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518378421</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L10" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M10" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -3109,19 +3126,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>2663415.63</v>
+        <v>5345297.55</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>285365.96035714285</v>
+        <v>572710.45178571425</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>2378049.6696428573</v>
+        <v>4772587.0982142864</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>23780.49669642857</v>
+        <v>47725.870982142864</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90930D43-6377-4DFC-BA04-779F4C77248C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F86FFF-C707-41AD-B071-6FCA5E246849}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="78">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>02/14/2026</t>
+  </si>
+  <si>
+    <t>02/16/2026</t>
   </si>
 </sst>
 </file>
@@ -2512,7 +2515,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2520,22 +2525,27 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518380796</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M11" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2547,7 +2557,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2555,22 +2567,27 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>518380603</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M12" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -3126,19 +3143,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>5345297.55</v>
+        <v>8027179.4699999997</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>572710.45178571425</v>
+        <v>860054.94321428565</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>4772587.0982142864</v>
+        <v>7167124.5267857155</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>47725.870982142864</v>
+        <v>71671.245267857157</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F86FFF-C707-41AD-B071-6FCA5E246849}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218E4789-1043-4A10-A731-E50BDE48453B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218E4789-1043-4A10-A731-E50BDE48453B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA53351-EAC3-4738-A9B7-26F6C9ED6154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="79">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>02/16/2026</t>
+  </si>
+  <si>
+    <t>02/20/2026</t>
   </si>
 </sst>
 </file>
@@ -2599,7 +2602,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2607,22 +2612,27 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518395700</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K13" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L13" s="27">
         <f>I13-K13</f>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M13" s="33">
         <f>I13/112</f>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -3143,19 +3153,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>8027179.4699999997</v>
+        <v>9368120.4299999997</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>860054.94321428565</v>
+        <v>1003727.1889285713</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>7167124.5267857155</v>
+        <v>8364393.24107143</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>71671.245267857157</v>
+        <v>83643.932410714304</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA53351-EAC3-4738-A9B7-26F6C9ED6154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172FD1E1-78AA-49C4-9C4F-6D01138C897B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172FD1E1-78AA-49C4-9C4F-6D01138C897B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661814A5-EBA2-4A7C-A27D-C6B85B52E4E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="80">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>02/20/2026</t>
+  </si>
+  <si>
+    <t>02/24/2026</t>
   </si>
 </sst>
 </file>
@@ -2644,7 +2647,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2652,22 +2657,27 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <v>518406817</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="38"/>
+      <c r="I14" s="38">
+        <f>1408216-56546.64</f>
+        <v>1351669.36</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>144821.71714285715</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1206847.642857143</v>
       </c>
       <c r="M14" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12068.47642857143</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -2679,7 +2689,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2687,22 +2699,27 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <v>518407191</v>
+      </c>
       <c r="H15" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="21">
+        <f>1403696-56546.64</f>
+        <v>1347149.36</v>
+      </c>
       <c r="K15" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>144337.43142857144</v>
       </c>
       <c r="L15" s="27">
         <f>I15-K15</f>
-        <v>0</v>
+        <v>1202811.9285714286</v>
       </c>
       <c r="M15" s="33">
         <f>I15/112</f>
-        <v>0</v>
+        <v>12028.119285714287</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3153,19 +3170,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>9368120.4299999997</v>
+        <v>12066939.149999999</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1003727.1889285713</v>
+        <v>1292886.3374999999</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>8364393.24107143</v>
+        <v>10774052.812500002</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>83643.932410714304</v>
+        <v>107740.52812500003</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{661814A5-EBA2-4A7C-A27D-C6B85B52E4E1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1ABECF-596C-4B44-BD23-672D7C5840B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="81">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>02/24/2026</t>
+  </si>
+  <si>
+    <t>02/25/2026</t>
   </si>
 </sst>
 </file>
@@ -2731,7 +2734,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2739,22 +2744,27 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518411379</v>
+      </c>
       <c r="H16" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="21">
+        <f>1358804-53836.69</f>
+        <v>1304967.31</v>
+      </c>
       <c r="K16" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>139817.92607142858</v>
       </c>
       <c r="L16" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1165149.3839285714</v>
       </c>
       <c r="M16" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11651.493839285715</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -3170,19 +3180,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>12066939.149999999</v>
+        <v>13371906.459999999</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1292886.3374999999</v>
+        <v>1432704.2635714286</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>10774052.812500002</v>
+        <v>11939202.196428573</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>107740.52812500003</v>
+        <v>119392.02196428574</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1ABECF-596C-4B44-BD23-672D7C5840B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98447F66-FED0-48FC-A02B-5498488238E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="82">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>02/25/2026</t>
+  </si>
+  <si>
+    <t>02/26/2026</t>
   </si>
 </sst>
 </file>
@@ -2776,7 +2779,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D17" s="20" t="s">
         <v>68</v>
       </c>
@@ -2784,22 +2789,27 @@
       <c r="F17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20">
+        <v>518415426</v>
+      </c>
       <c r="H17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="21">
+        <f>1365120-87540.06</f>
+        <v>1277579.94</v>
+      </c>
       <c r="K17" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>136883.565</v>
       </c>
       <c r="L17" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1140696.375</v>
       </c>
       <c r="M17" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11406.963749999999</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -3180,19 +3190,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>13371906.459999999</v>
+        <v>14649486.399999999</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1432704.2635714286</v>
+        <v>1569587.8285714285</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>11939202.196428573</v>
+        <v>13079898.571428573</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>119392.02196428574</v>
+        <v>130798.98571428574</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98447F66-FED0-48FC-A02B-5498488238E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C12456-D46B-4A7B-8D56-087F6A96F056}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="83">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>02/26/2026</t>
+  </si>
+  <si>
+    <t>02/27/2026</t>
   </si>
 </sst>
 </file>
@@ -2821,7 +2824,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D18" s="20" t="s">
         <v>68</v>
       </c>
@@ -2829,22 +2834,27 @@
       <c r="F18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20">
+        <v>518420061</v>
+      </c>
       <c r="H18" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="21">
+        <f>1300442-53176.24</f>
+        <v>1247265.76</v>
+      </c>
       <c r="K18" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>133635.61714285714</v>
       </c>
       <c r="L18" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1113630.142857143</v>
       </c>
       <c r="M18" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11136.301428571429</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -3190,19 +3200,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>14649486.399999999</v>
+        <v>15896752.159999998</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1569587.8285714285</v>
+        <v>1703223.4457142856</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>13079898.571428573</v>
+        <v>14193528.714285716</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>130798.98571428574</v>
+        <v>141935.28714285715</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/PURCHASES - FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C12456-D46B-4A7B-8D56-087F6A96F056}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33022E4-9F09-49D2-91B4-62F9129AF2CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="84">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>02/27/2026</t>
+  </si>
+  <si>
+    <t>02/28/2026</t>
   </si>
 </sst>
 </file>
@@ -2866,7 +2869,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
@@ -2874,22 +2879,27 @@
       <c r="F19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20">
+        <v>518425142</v>
+      </c>
       <c r="H19" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="21">
+        <f>259108-22772.64</f>
+        <v>236335.35999999999</v>
+      </c>
       <c r="K19" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25321.645714285714</v>
       </c>
       <c r="L19" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>211013.71428571426</v>
       </c>
       <c r="M19" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2110.1371428571429</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -2901,7 +2911,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="D20" s="20" t="s">
         <v>68</v>
       </c>
@@ -2909,22 +2921,28 @@
       <c r="F20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="20">
+        <f>518425044</f>
+        <v>518425044</v>
+      </c>
       <c r="H20" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K20" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L20" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -2936,7 +2954,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C21" s="19"/>
+      <c r="C21" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="D21" s="20" t="s">
         <v>68</v>
       </c>
@@ -2944,22 +2964,27 @@
       <c r="F21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="20">
+        <v>518425107</v>
+      </c>
       <c r="H21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="21">
+        <f>244922-8385.01</f>
+        <v>236536.99</v>
+      </c>
       <c r="K21" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>25343.248928571429</v>
       </c>
       <c r="L21" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>211193.74107142855</v>
       </c>
       <c r="M21" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2111.9374107142858</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -2971,7 +2996,9 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C22" s="19"/>
+      <c r="C22" s="19" t="s">
+        <v>83</v>
+      </c>
       <c r="D22" s="20" t="s">
         <v>68</v>
       </c>
@@ -2979,22 +3006,27 @@
       <c r="F22" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="20">
+        <v>518425261</v>
+      </c>
       <c r="H22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="21">
+        <f>1397196-56255.04</f>
+        <v>1340940.96</v>
+      </c>
       <c r="K22" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143672.2457142857</v>
       </c>
       <c r="L22" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1197268.7142857143</v>
       </c>
       <c r="M22" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11972.687142857143</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3200,19 +3232,19 @@
       <c r="G32"/>
       <c r="I32" s="14">
         <f>SUM(I7:I31)</f>
-        <v>15896752.159999998</v>
+        <v>19051506.429999996</v>
       </c>
       <c r="K32" s="14">
         <f>SUM(K7:K31)</f>
-        <v>1703223.4457142856</v>
+        <v>2041232.831785714</v>
       </c>
       <c r="L32" s="14">
         <f>SUM(L7:L31)</f>
-        <v>14193528.714285716</v>
+        <v>17010273.598214287</v>
       </c>
       <c r="M32" s="36">
         <f>SUM(M7:M31)</f>
-        <v>141935.28714285715</v>
+        <v>170102.73598214285</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
